--- a/data/data/ICICI Prudential Mutual Fund/ICICI Prudential Nifty 100 Low Volatility 30 ETF FOF.xlsx
+++ b/data/data/ICICI Prudential Mutual Fund/ICICI Prudential Nifty 100 Low Volatility 30 ETF FOF.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="51" uniqueCount="26">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="50" uniqueCount="25">
   <si>
     <t>ICICI Prudential Mutual Fund</t>
   </si>
@@ -22,7 +22,7 @@
     <t>ICICI Prudential Nifty 100 Low Volatility 30 ETF FOF</t>
   </si>
   <si>
-    <t>Portfolio as on Jan 31,2025</t>
+    <t>Portfolio as on May 31,2025</t>
   </si>
   <si>
     <t>Company/Issuer/Instrument Name</t>
@@ -79,7 +79,7 @@
     <t>@ As per AMFI Best Practices Guidelines Circular No. 91/ 2020 - 21 dated March 24, 2021 on Valuation of AT-1 Bonds and Tier 2 Bonds, Yield to call is disclosed for AT-1 Bonds and Tier 2 Bonds issued by Banks as provided by Valuation agencies.</t>
   </si>
   <si>
-    <t>For Instances of Deviation In valuation Of Securities as per SEBI master circular ref no SEBI/HO/IMD/IMD-PoD-1/P/CIR/2023/74 dated May 19, 2023.Refer link: https://www.icicipruamc.com/statutory-disclosures/deviation-in-valuation-of-securities</t>
+    <t>For Instances of Deviation In valuation Of Securities as per SEBI master circular ref no SEBI/HO/IMD/IMD-PoD-1/P/CIR/2024/90 dated June 27, 2024. Refer link: https://www.icicipruamc.com/about-us/statutory-disclosures?currentTabFilter=OtherDisclosures&amp;&amp;subCatTabFilter=deviationinvaluationofsecurities</t>
   </si>
   <si>
     <t>As per AMFI Best Practices Guidelines Circular No. AMFI/ 35P/ MEM-COR/ 72 / 2022-23 dated December 31, 2022 on Standard format for disclosure Portfolio YTM for Debt Schemes, Yield of the instrument is disclosed on annualized basis as provided by Valuation agencies.</t>
@@ -89,9 +89,6 @@
   </si>
   <si>
     <t>Benchmark Riskometer</t>
-  </si>
-  <si>
-    <t>Benchmark name - Nifty 100 Low Volatility 30 TRI</t>
   </si>
 </sst>
 </file>
@@ -791,7 +788,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-  <dimension ref="B1:J36"/>
+  <dimension ref="B1:J35"/>
   <sheetFormatPr defaultColWidth="10" defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" customWidth="true" style="21" width="10.0" collapsed="true"/>
@@ -885,10 +882,10 @@
         <v>12</v>
       </c>
       <c r="F5" s="9">
-        <v>140934.56</v>
+        <v>147448.54</v>
       </c>
       <c r="G5" s="10">
-        <v>0.9996916010717</v>
+        <v>0.999098249715</v>
       </c>
       <c r="H5" s="9" t="s">
         <v>12</v>
@@ -908,13 +905,13 @@
         <v>15</v>
       </c>
       <c r="E6" s="14">
-        <v>671756716</v>
+        <v>687405767</v>
       </c>
       <c r="F6" s="15">
-        <v>140934.56</v>
+        <v>147448.54</v>
       </c>
       <c r="G6" s="16">
-        <v>0.9996916010717</v>
+        <v>0.999098249715</v>
       </c>
       <c r="H6" s="15" t="s">
         <v>12</v>
@@ -945,10 +942,10 @@
         <v>12</v>
       </c>
       <c r="F8" s="9">
-        <v>161.61</v>
+        <v>172.15</v>
       </c>
       <c r="G8" s="10">
-        <v>0.001146348771</v>
+        <v>0.0011664731552</v>
       </c>
       <c r="H8" s="9" t="s">
         <v>12</v>
@@ -979,10 +976,10 @@
         <v>12</v>
       </c>
       <c r="F10" s="18">
-        <v>-118.13252432999434</v>
+        <v>-39.068230509990826</v>
       </c>
       <c r="G10" s="19">
-        <v>-0.0008379498427220032</v>
+        <v>-0.0002647228702433701</v>
       </c>
       <c r="H10" s="18" t="s">
         <v>12</v>
@@ -1005,10 +1002,10 @@
         <v>12</v>
       </c>
       <c r="F11" s="18">
-        <v>140978.03747567</v>
+        <v>147581.62176949</v>
       </c>
       <c r="G11" s="19">
-        <v>0.9999999999999779</v>
+        <v>0.9999999999999567</v>
       </c>
       <c r="H11" s="18" t="s">
         <v>12</v>
@@ -1045,11 +1042,6 @@
     <row r="35" ht="15">
       <c r="B35" s="21" t="s">
         <v>24</v>
-      </c>
-    </row>
-    <row r="36" ht="15">
-      <c r="B36" s="21" t="s">
-        <v>25</v>
       </c>
     </row>
   </sheetData>
